--- a/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_요구사항정의서.xlsx
+++ b/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_요구사항정의서.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
-  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
+  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
+  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="8970"/>
   </bookViews>
   <sheets>
-    <sheet name="20260428_요구사항정의서" sheetId="1" r:id="rId1"/>
+    <sheet sheetId="1" name="20260428_요구사항정의서" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr calcId="171027"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="151" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="121">
   <si>
     <t>● 요구사항 정의서</t>
   </si>
@@ -341,6 +341,42 @@
   </si>
   <si>
     <t>Node.js, Express, MySQL 8.0, Vanilla JS 기반 환경</t>
+  </si>
+  <si>
+    <t>쿠폰 발급 수량 제어</t>
+  </si>
+  <si>
+    <t>관리자가 쿠폰별 총 발급 수량을 동적으로 설정 가능</t>
+  </si>
+  <si>
+    <t>구현완료</t>
+  </si>
+  <si>
+    <t>FR-12</t>
+  </si>
+  <si>
+    <t>쿠폰 발급 대상 확장</t>
+  </si>
+  <si>
+    <t>리뷰 작성자 타겟팅 발급 기능</t>
+  </si>
+  <si>
+    <t>FR-13</t>
+  </si>
+  <si>
+    <t>프로모션 코드 연동</t>
+  </si>
+  <si>
+    <t>쿠폰별 고유 영문 코드 매핑</t>
+  </si>
+  <si>
+    <t>FR-14</t>
+  </si>
+  <si>
+    <t>자동 회원 등급제</t>
+  </si>
+  <si>
+    <t>구매 금액별 등급 자동 승급 로직</t>
   </si>
 </sst>
 </file>
@@ -349,32 +385,32 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <color theme="1"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+      <sz val="11"/>
+      <name val="맑은 고딕"/>
     </font>
     <font>
       <b/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="14"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
     </font>
     <font>
       <b/>
+      <charset val="129"/>
+      <family val="3"/>
       <sz val="11"/>
       <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-    </font>
-    <font>
-      <sz val="8"/>
-      <name val="맑은 고딕"/>
-      <family val="3"/>
-      <charset val="129"/>
-      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -399,18 +435,10 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
+      <left style="thin"/>
+      <right style="thin"/>
+      <top style="thin"/>
+      <bottom style="thin"/>
       <diagonal/>
     </border>
   </borders>
@@ -419,27 +447,27 @@
   </cellStyleXfs>
   <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="표준" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -717,522 +745,577 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="B1:K17"/>
-  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:K21"/>
+  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
   <cols>
     <col min="1" max="1" width="1.625" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="23.875" style="6" customWidth="1"/>
+    <col min="4" max="4" width="23.875" style="1" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="15" style="6" customWidth="1"/>
+    <col min="6" max="6" width="15" style="1" customWidth="1"/>
     <col min="7" max="7" width="46.75" customWidth="1"/>
-    <col min="8" max="8" width="20.25" style="6" customWidth="1"/>
+    <col min="8" max="8" width="20.25" style="1" customWidth="1"/>
     <col min="9" max="9" width="18.375" customWidth="1"/>
     <col min="10" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="10" style="6" customWidth="1"/>
+    <col min="11" max="11" width="10" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B1" s="4" t="s">
+    <row r="1" ht="20.25" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B1" s="2" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="4"/>
-      <c r="D1" s="4"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="4"/>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B3" s="1" t="s">
+      <c r="C1" s="2"/>
+      <c r="D1" s="2"/>
+      <c r="E1" s="2"/>
+      <c r="F1" s="2"/>
+      <c r="G1" s="2"/>
+      <c r="H1" s="2"/>
+      <c r="I1" s="2"/>
+      <c r="J1" s="2"/>
+      <c r="K1" s="2"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B3" s="3" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" s="3" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="3" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="3" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" s="3" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" s="3" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B4" s="2" t="s">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B4" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="C4" s="4" t="s">
         <v>12</v>
       </c>
       <c r="D4" s="5" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="2" t="s">
+      <c r="E4" s="4" t="s">
         <v>14</v>
       </c>
       <c r="F4" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="3" t="s">
+      <c r="G4" s="6" t="s">
         <v>16</v>
       </c>
       <c r="H4" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="3" t="s">
+      <c r="I4" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="2" t="s">
+      <c r="J4" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K4" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B5" s="2" t="s">
+    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B5" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="C5" s="4" t="s">
         <v>21</v>
       </c>
       <c r="D5" s="5" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="E5" s="4" t="s">
         <v>23</v>
       </c>
       <c r="F5" s="5" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="3" t="s">
+      <c r="G5" s="6" t="s">
         <v>25</v>
       </c>
       <c r="H5" s="5" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="3" t="s">
+      <c r="I5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="2" t="s">
+      <c r="J5" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K5" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B6" s="2" t="s">
+    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B6" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="C6" s="4" t="s">
         <v>28</v>
       </c>
       <c r="D6" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="E6" s="4" t="s">
         <v>30</v>
       </c>
       <c r="F6" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="3" t="s">
+      <c r="G6" s="6" t="s">
         <v>32</v>
       </c>
       <c r="H6" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="3" t="s">
+      <c r="I6" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="2" t="s">
+      <c r="J6" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K6" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B7" s="2" t="s">
+    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B7" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="C7" s="4" t="s">
         <v>35</v>
       </c>
       <c r="D7" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="2" t="s">
+      <c r="E7" s="4" t="s">
         <v>37</v>
       </c>
       <c r="F7" s="5" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="3" t="s">
+      <c r="G7" s="6" t="s">
         <v>39</v>
       </c>
       <c r="H7" s="5" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="3" t="s">
+      <c r="I7" s="6" t="s">
         <v>41</v>
       </c>
-      <c r="J7" s="2" t="s">
+      <c r="J7" s="4" t="s">
         <v>42</v>
       </c>
       <c r="K7" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="2:11" ht="33" x14ac:dyDescent="0.3">
-      <c r="B8" s="2" t="s">
+    <row r="8" ht="33" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B8" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="2" t="s">
+      <c r="C8" s="4" t="s">
         <v>43</v>
       </c>
       <c r="D8" s="5" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="2" t="s">
+      <c r="E8" s="4" t="s">
         <v>45</v>
       </c>
       <c r="F8" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="3" t="s">
+      <c r="G8" s="6" t="s">
         <v>47</v>
       </c>
       <c r="H8" s="5" t="s">
         <v>48</v>
       </c>
-      <c r="I8" s="3" t="s">
+      <c r="I8" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="2" t="s">
+      <c r="J8" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K8" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="2:11" ht="33" x14ac:dyDescent="0.3">
-      <c r="B9" s="2" t="s">
+    <row r="9" ht="33" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B9" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="2" t="s">
+      <c r="C9" s="4" t="s">
         <v>50</v>
       </c>
       <c r="D9" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="2" t="s">
+      <c r="E9" s="4" t="s">
         <v>52</v>
       </c>
       <c r="F9" s="5" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="3" t="s">
+      <c r="G9" s="6" t="s">
         <v>54</v>
       </c>
       <c r="H9" s="5" t="s">
         <v>55</v>
       </c>
-      <c r="I9" s="3" t="s">
+      <c r="I9" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="J9" s="2" t="s">
+      <c r="J9" s="4" t="s">
         <v>42</v>
       </c>
       <c r="K9" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="2:11" ht="33" x14ac:dyDescent="0.3">
-      <c r="B10" s="2" t="s">
+    <row r="10" ht="33" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B10" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="2" t="s">
+      <c r="C10" s="4" t="s">
         <v>57</v>
       </c>
       <c r="D10" s="5" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="2" t="s">
+      <c r="E10" s="4" t="s">
         <v>59</v>
       </c>
       <c r="F10" s="5" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="3" t="s">
+      <c r="G10" s="6" t="s">
         <v>61</v>
       </c>
       <c r="H10" s="5" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="3" t="s">
+      <c r="I10" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="2" t="s">
+      <c r="J10" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K10" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="2:11" ht="33" x14ac:dyDescent="0.3">
-      <c r="B11" s="2" t="s">
+    <row r="11" ht="33" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B11" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="2" t="s">
+      <c r="C11" s="4" t="s">
         <v>64</v>
       </c>
       <c r="D11" s="5" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="2" t="s">
+      <c r="E11" s="4" t="s">
         <v>66</v>
       </c>
       <c r="F11" s="5" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="3" t="s">
+      <c r="G11" s="6" t="s">
         <v>68</v>
       </c>
       <c r="H11" s="5" t="s">
         <v>69</v>
       </c>
-      <c r="I11" s="3" t="s">
+      <c r="I11" s="6" t="s">
         <v>70</v>
       </c>
-      <c r="J11" s="2" t="s">
+      <c r="J11" s="4" t="s">
         <v>42</v>
       </c>
       <c r="K11" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="2:11" ht="33" x14ac:dyDescent="0.3">
-      <c r="B12" s="2" t="s">
+    <row r="12" ht="33" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B12" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="4" t="s">
         <v>71</v>
       </c>
       <c r="D12" s="5" t="s">
         <v>72</v>
       </c>
-      <c r="E12" s="2" t="s">
+      <c r="E12" s="4" t="s">
         <v>73</v>
       </c>
       <c r="F12" s="5" t="s">
         <v>74</v>
       </c>
-      <c r="G12" s="3" t="s">
+      <c r="G12" s="6" t="s">
         <v>75</v>
       </c>
       <c r="H12" s="5" t="s">
         <v>76</v>
       </c>
-      <c r="I12" s="3" t="s">
+      <c r="I12" s="6" t="s">
         <v>77</v>
       </c>
-      <c r="J12" s="2" t="s">
+      <c r="J12" s="4" t="s">
         <v>42</v>
       </c>
       <c r="K12" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="2:11" ht="33" x14ac:dyDescent="0.3">
-      <c r="B13" s="2" t="s">
+    <row r="13" ht="33" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B13" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="4" t="s">
         <v>78</v>
       </c>
       <c r="D13" s="5" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="2" t="s">
+      <c r="E13" s="4" t="s">
         <v>80</v>
       </c>
       <c r="F13" s="5" t="s">
         <v>81</v>
       </c>
-      <c r="G13" s="3" t="s">
+      <c r="G13" s="6" t="s">
         <v>82</v>
       </c>
       <c r="H13" s="5" t="s">
         <v>83</v>
       </c>
-      <c r="I13" s="3" t="s">
+      <c r="I13" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="J13" s="2" t="s">
+      <c r="J13" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K13" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="2:11" ht="33" x14ac:dyDescent="0.3">
-      <c r="B14" s="2" t="s">
+    <row r="14" ht="33" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B14" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="4" t="s">
         <v>85</v>
       </c>
       <c r="D14" s="5" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="2" t="s">
+      <c r="E14" s="4" t="s">
         <v>87</v>
       </c>
       <c r="F14" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="3" t="s">
+      <c r="G14" s="6" t="s">
         <v>89</v>
       </c>
       <c r="H14" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="I14" s="3" t="s">
+      <c r="I14" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="J14" s="2" t="s">
+      <c r="J14" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K14" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="2:11" ht="33" x14ac:dyDescent="0.3">
-      <c r="B15" s="2" t="s">
+    <row r="15" ht="33" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B15" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="4" t="s">
         <v>93</v>
       </c>
       <c r="D15" s="5" t="s">
         <v>94</v>
       </c>
-      <c r="E15" s="2" t="s">
+      <c r="E15" s="4" t="s">
         <v>95</v>
       </c>
       <c r="F15" s="5" t="s">
         <v>96</v>
       </c>
-      <c r="G15" s="3" t="s">
+      <c r="G15" s="6" t="s">
         <v>97</v>
       </c>
       <c r="H15" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" s="2" t="s">
+      <c r="I15" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K15" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B16" s="2" t="s">
+    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B16" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="4" t="s">
         <v>98</v>
       </c>
       <c r="D16" s="5" t="s">
         <v>99</v>
       </c>
-      <c r="E16" s="2" t="s">
+      <c r="E16" s="4" t="s">
         <v>100</v>
       </c>
       <c r="F16" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="G16" s="3" t="s">
+      <c r="G16" s="6" t="s">
         <v>102</v>
       </c>
       <c r="H16" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I16" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="2" t="s">
+      <c r="I16" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K16" s="5" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B17" s="2" t="s">
+    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
+      <c r="B17" s="4" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="4" t="s">
         <v>104</v>
       </c>
       <c r="D17" s="5" t="s">
         <v>105</v>
       </c>
-      <c r="E17" s="2" t="s">
+      <c r="E17" s="4" t="s">
         <v>106</v>
       </c>
       <c r="F17" s="5" t="s">
         <v>107</v>
       </c>
-      <c r="G17" s="3" t="s">
+      <c r="G17" s="6" t="s">
         <v>108</v>
       </c>
       <c r="H17" s="5" t="s">
         <v>20</v>
       </c>
-      <c r="I17" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="2" t="s">
+      <c r="I17" s="6" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="4" t="s">
         <v>19</v>
       </c>
       <c r="K17" s="5" t="s">
         <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>85</v>
+      </c>
+      <c r="B18" t="s">
+        <v>109</v>
+      </c>
+      <c r="C18" t="s">
+        <v>110</v>
+      </c>
+      <c r="D18" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>112</v>
+      </c>
+      <c r="B19" t="s">
+        <v>113</v>
+      </c>
+      <c r="C19" t="s">
+        <v>114</v>
+      </c>
+      <c r="D19" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A20" t="s">
+        <v>115</v>
+      </c>
+      <c r="B20" t="s">
+        <v>116</v>
+      </c>
+      <c r="C20" t="s">
+        <v>117</v>
+      </c>
+      <c r="D20" s="1" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A21" t="s">
+        <v>118</v>
+      </c>
+      <c r="B21" t="s">
+        <v>119</v>
+      </c>
+      <c r="C21" t="s">
+        <v>120</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>111</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:K1"/>
   </mergeCells>
-  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
 </file>
--- a/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_요구사항정의서.xlsx
+++ b/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_요구사항정의서.xlsx
@@ -1,20 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
-  <workbookPr defaultThemeVersion="164011" filterPrivacy="1"/>
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="5" rupBuild="14420"/>
+  <workbookPr filterPrivacy="1" defaultThemeVersion="164011"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="20400" windowHeight="8970"/>
   </bookViews>
   <sheets>
-    <sheet sheetId="1" name="20260428_요구사항정의서" state="visible" r:id="rId4"/>
+    <sheet name="20260428_요구사항정의서" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="171027"/>
+  <calcPr calcId="162913"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="167" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="137">
   <si>
     <t>● 요구사항 정의서</t>
   </si>
@@ -343,40 +343,116 @@
     <t>Node.js, Express, MySQL 8.0, Vanilla JS 기반 환경</t>
   </si>
   <si>
+    <t>FR</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FR-12</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
     <t>쿠폰 발급 수량 제어</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-12</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿠폰 관리</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>관리자가 쿠폰별 총 발급 수량을 동적으로 설정 가능</t>
-  </si>
-  <si>
-    <t>구현완료</t>
-  </si>
-  <si>
-    <t>FR-12</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>설정값</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>업데이트된 쿠폰</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>상</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>-</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FR-13</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>쿠폰 발급 대상 확장</t>
-  </si>
-  <si>
-    <t>리뷰 작성자 타겟팅 발급 기능</t>
-  </si>
-  <si>
-    <t>FR-13</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿠폰 관리</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>리뷰 작성자 타겟팅 발급 기능 제공</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>대상 선택</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FR-14</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>프로모션 코드 연동</t>
-  </si>
-  <si>
-    <t>쿠폰별 고유 영문 코드 매핑</t>
-  </si>
-  <si>
-    <t>FR-14</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>쿠폰별 고유 영문 프로모션 코드 매핑</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>코드 입력</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>중</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>FR-15</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
   <si>
     <t>자동 회원 등급제</t>
-  </si>
-  <si>
-    <t>구매 금액별 등급 자동 승급 로직</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>F-13</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>회원 관리</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>누적 구매 금액별 등급 자동 승급 로직 적용</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>구매 금액</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>갱신된 등급</t>
+    <phoneticPr fontId="3" type="noConversion"/>
+  </si>
+  <si>
+    <t>상</t>
+    <phoneticPr fontId="3" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -385,32 +461,32 @@
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="맑은 고딕"/>
       <family val="2"/>
       <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <color theme="1"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-      <sz val="11"/>
-      <name val="맑은 고딕"/>
     </font>
     <font>
       <b/>
-      <charset val="129"/>
-      <family val="3"/>
       <sz val="14"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
     </font>
     <font>
       <b/>
-      <charset val="129"/>
-      <family val="3"/>
       <sz val="11"/>
       <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+    </font>
+    <font>
+      <sz val="8"/>
+      <name val="맑은 고딕"/>
+      <family val="3"/>
+      <charset val="129"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="3">
@@ -435,39 +511,56 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin"/>
-      <right style="thin"/>
-      <top style="thin"/>
-      <bottom style="thin"/>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="표준" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -745,577 +838,650 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K21"/>
-  <sheetFormatPr defaultRowHeight="16.5" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="0.3" customHeight="1"/>
+  <dimension ref="B1:K21"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="1.625" customWidth="1"/>
     <col min="2" max="2" width="8" customWidth="1"/>
     <col min="3" max="3" width="12" customWidth="1"/>
-    <col min="4" max="4" width="23.875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="23.875" style="5" customWidth="1"/>
     <col min="5" max="5" width="8" customWidth="1"/>
-    <col min="6" max="6" width="15" style="1" customWidth="1"/>
+    <col min="6" max="6" width="15" style="5" customWidth="1"/>
     <col min="7" max="7" width="46.75" customWidth="1"/>
-    <col min="8" max="8" width="20.25" style="1" customWidth="1"/>
+    <col min="8" max="8" width="20.25" style="5" customWidth="1"/>
     <col min="9" max="9" width="18.375" customWidth="1"/>
     <col min="10" max="10" width="8" customWidth="1"/>
-    <col min="11" max="11" width="10" style="1" customWidth="1"/>
+    <col min="11" max="11" width="10" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" ht="20.25" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B1" s="2" t="s">
+    <row r="1" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
+      <c r="B1" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="2"/>
-      <c r="D1" s="2"/>
-      <c r="E1" s="2"/>
-      <c r="F1" s="2"/>
-      <c r="G1" s="2"/>
-      <c r="H1" s="2"/>
-      <c r="I1" s="2"/>
-      <c r="J1" s="2"/>
-      <c r="K1" s="2"/>
-    </row>
-    <row r="3" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B3" s="3" t="s">
+      <c r="C1" s="6"/>
+      <c r="D1" s="6"/>
+      <c r="E1" s="6"/>
+      <c r="F1" s="6"/>
+      <c r="G1" s="6"/>
+      <c r="H1" s="6"/>
+      <c r="I1" s="6"/>
+      <c r="J1" s="6"/>
+      <c r="K1" s="6"/>
+    </row>
+    <row r="3" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B3" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C3" s="3" t="s">
+      <c r="C3" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="s">
+      <c r="D3" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E3" s="3" t="s">
+      <c r="E3" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F3" s="3" t="s">
+      <c r="F3" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="G3" s="3" t="s">
+      <c r="G3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="H3" s="3" t="s">
+      <c r="H3" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="I3" s="3" t="s">
+      <c r="I3" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="J3" s="3" t="s">
+      <c r="J3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="K3" s="3" t="s">
+      <c r="K3" s="1" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B4" s="4" t="s">
+    <row r="4" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B4" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="D4" s="5" t="s">
+      <c r="D4" s="4" t="s">
         <v>13</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F4" s="5" t="s">
+      <c r="F4" s="4" t="s">
         <v>15</v>
       </c>
-      <c r="G4" s="6" t="s">
+      <c r="G4" s="3" t="s">
         <v>16</v>
       </c>
-      <c r="H4" s="5" t="s">
+      <c r="H4" s="4" t="s">
         <v>17</v>
       </c>
-      <c r="I4" s="6" t="s">
+      <c r="I4" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="J4" s="4" t="s">
+      <c r="J4" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K4" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="5" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B5" s="4" t="s">
+      <c r="K4" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="5" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B5" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="D5" s="5" t="s">
+      <c r="D5" s="4" t="s">
         <v>22</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="5" t="s">
+      <c r="F5" s="4" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="6" t="s">
+      <c r="G5" s="3" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="5" t="s">
+      <c r="H5" s="4" t="s">
         <v>26</v>
       </c>
-      <c r="I5" s="6" t="s">
+      <c r="I5" s="3" t="s">
         <v>27</v>
       </c>
-      <c r="J5" s="4" t="s">
+      <c r="J5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K5" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="6" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B6" s="4" t="s">
+      <c r="K5" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="6" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B6" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D6" s="5" t="s">
+      <c r="D6" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="E6" s="4" t="s">
+      <c r="E6" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F6" s="5" t="s">
+      <c r="F6" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="G6" s="6" t="s">
+      <c r="G6" s="3" t="s">
         <v>32</v>
       </c>
-      <c r="H6" s="5" t="s">
+      <c r="H6" s="4" t="s">
         <v>33</v>
       </c>
-      <c r="I6" s="6" t="s">
+      <c r="I6" s="3" t="s">
         <v>34</v>
       </c>
-      <c r="J6" s="4" t="s">
+      <c r="J6" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K6" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="7" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B7" s="4" t="s">
+      <c r="K6" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="D7" s="5" t="s">
+      <c r="D7" s="4" t="s">
         <v>36</v>
       </c>
-      <c r="E7" s="4" t="s">
+      <c r="E7" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="F7" s="5" t="s">
+      <c r="F7" s="4" t="s">
         <v>38</v>
       </c>
-      <c r="G7" s="6" t="s">
+      <c r="G7" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="H7" s="5" t="s">
+      <c r="H7" s="4" t="s">
         <v>40</v>
       </c>
-      <c r="I7" s="6" t="s">
+      <c r="I7" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="J7" s="4" t="s">
+      <c r="J7" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K7" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="8" ht="33" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B8" s="4" t="s">
+      <c r="K7" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="8" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="D8" s="5" t="s">
+      <c r="D8" s="4" t="s">
         <v>44</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="F8" s="5" t="s">
+      <c r="F8" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="G8" s="6" t="s">
+      <c r="G8" s="3" t="s">
         <v>47</v>
       </c>
-      <c r="H8" s="5" t="s">
+      <c r="H8" s="4" t="s">
         <v>48</v>
       </c>
-      <c r="I8" s="6" t="s">
+      <c r="I8" s="3" t="s">
         <v>49</v>
       </c>
-      <c r="J8" s="4" t="s">
+      <c r="J8" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K8" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="9" ht="33" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B9" s="4" t="s">
+      <c r="K8" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="9" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D9" s="5" t="s">
+      <c r="D9" s="4" t="s">
         <v>51</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="F9" s="5" t="s">
+      <c r="F9" s="4" t="s">
         <v>53</v>
       </c>
-      <c r="G9" s="6" t="s">
+      <c r="G9" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="H9" s="5" t="s">
+      <c r="H9" s="4" t="s">
         <v>55</v>
       </c>
-      <c r="I9" s="6" t="s">
+      <c r="I9" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="J9" s="4" t="s">
+      <c r="J9" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K9" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="10" ht="33" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B10" s="4" t="s">
+      <c r="K9" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="10" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="5" t="s">
+      <c r="D10" s="4" t="s">
         <v>58</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="F10" s="5" t="s">
+      <c r="F10" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="G10" s="6" t="s">
+      <c r="G10" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="H10" s="5" t="s">
+      <c r="H10" s="4" t="s">
         <v>62</v>
       </c>
-      <c r="I10" s="6" t="s">
+      <c r="I10" s="3" t="s">
         <v>63</v>
       </c>
-      <c r="J10" s="4" t="s">
+      <c r="J10" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K10" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="11" ht="33" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B11" s="4" t="s">
+      <c r="K10" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="11" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B11" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="D11" s="5" t="s">
+      <c r="D11" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F11" s="5" t="s">
+      <c r="F11" s="4" t="s">
         <v>67</v>
       </c>
-      <c r="G11" s="6" t="s">
+      <c r="G11" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="H11" s="5" t="s">
+      <c r="H11" s="4" t="s">
         <v>69</v>
       </c>
-      <c r="I11" s="6" t="s">
+      <c r="I11" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="J11" s="4" t="s">
+      <c r="J11" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K11" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="12" ht="33" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B12" s="4" t="s">
+      <c r="K11" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="12" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B12" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="D12" s="5" t="s">
+      <c r="D12" s="4" t="s">
         <v>72</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="F12" s="5" t="s">
+      <c r="F12" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="G12" s="6" t="s">
+      <c r="G12" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="H12" s="5" t="s">
+      <c r="H12" s="4" t="s">
         <v>76</v>
       </c>
-      <c r="I12" s="6" t="s">
+      <c r="I12" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="J12" s="4" t="s">
+      <c r="J12" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="K12" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="13" ht="33" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B13" s="4" t="s">
+      <c r="K12" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="13" spans="2:11" ht="33" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="D13" s="5" t="s">
+      <c r="D13" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="F13" s="5" t="s">
+      <c r="F13" s="4" t="s">
         <v>81</v>
       </c>
-      <c r="G13" s="6" t="s">
+      <c r="G13" s="3" t="s">
         <v>82</v>
       </c>
-      <c r="H13" s="5" t="s">
+      <c r="H13" s="4" t="s">
         <v>83</v>
       </c>
-      <c r="I13" s="6" t="s">
+      <c r="I13" s="3" t="s">
         <v>84</v>
       </c>
-      <c r="J13" s="4" t="s">
+      <c r="J13" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K13" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="14" ht="33" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B14" s="4" t="s">
+      <c r="K13" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="5" t="s">
+      <c r="D14" s="4" t="s">
         <v>86</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="F14" s="5" t="s">
+      <c r="F14" s="4" t="s">
         <v>88</v>
       </c>
-      <c r="G14" s="6" t="s">
+      <c r="G14" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="H14" s="5" t="s">
+      <c r="H14" s="4" t="s">
         <v>90</v>
       </c>
-      <c r="I14" s="6" t="s">
+      <c r="I14" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="J14" s="4" t="s">
+      <c r="J14" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K14" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="15" ht="33" customHeight="1" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B15" s="4" t="s">
+      <c r="K14" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="D15" s="5" t="s">
+      <c r="D15" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="F15" s="5" t="s">
+      <c r="F15" s="4" t="s">
         <v>96</v>
       </c>
-      <c r="G15" s="6" t="s">
+      <c r="G15" s="3" t="s">
         <v>97</v>
       </c>
-      <c r="H15" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I15" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J15" s="4" t="s">
+      <c r="H15" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I15" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J15" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K15" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="16" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B16" s="4" t="s">
+      <c r="K15" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="16" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B16" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="D16" s="5" t="s">
+      <c r="D16" s="4" t="s">
         <v>99</v>
       </c>
-      <c r="E16" s="4" t="s">
+      <c r="E16" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F16" s="5" t="s">
+      <c r="F16" s="4" t="s">
         <v>101</v>
       </c>
-      <c r="G16" s="6" t="s">
+      <c r="G16" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="H16" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I16" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J16" s="4" t="s">
+      <c r="H16" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I16" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J16" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K16" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="17" spans="2:11" x14ac:dyDescent="0.25">
-      <c r="B17" s="4" t="s">
+      <c r="K16" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="17" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B17" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="D17" s="5" t="s">
+      <c r="D17" s="4" t="s">
         <v>105</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="F17" s="5" t="s">
+      <c r="F17" s="4" t="s">
         <v>107</v>
       </c>
-      <c r="G17" s="6" t="s">
+      <c r="G17" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="H17" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="I17" s="6" t="s">
-        <v>20</v>
-      </c>
-      <c r="J17" s="4" t="s">
+      <c r="H17" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="I17" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="J17" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="K17" s="5" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="18" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>85</v>
-      </c>
-      <c r="B18" t="s">
+      <c r="K17" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B18" s="7" t="s">
         <v>109</v>
       </c>
-      <c r="C18" t="s">
+      <c r="C18" s="7" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="8" t="s">
         <v>111</v>
       </c>
-    </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
+      <c r="E18" s="7" t="s">
         <v>112</v>
       </c>
-      <c r="B19" t="s">
+      <c r="F18" s="8" t="s">
         <v>113</v>
       </c>
-      <c r="C19" t="s">
+      <c r="G18" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="D19" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A20" t="s">
+      <c r="H18" s="8" t="s">
         <v>115</v>
       </c>
-      <c r="B20" t="s">
+      <c r="I18" s="9" t="s">
         <v>116</v>
       </c>
-      <c r="C20" t="s">
+      <c r="J18" s="7" t="s">
         <v>117</v>
       </c>
-      <c r="D20" s="1" t="s">
-        <v>111</v>
-      </c>
-    </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.25">
-      <c r="A21" t="s">
+      <c r="K18" s="8" t="s">
         <v>118</v>
       </c>
-      <c r="B21" t="s">
+    </row>
+    <row r="19" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B19" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C19" s="7" t="s">
         <v>119</v>
       </c>
-      <c r="C21" t="s">
+      <c r="D19" s="8" t="s">
         <v>120</v>
       </c>
-      <c r="D21" s="1" t="s">
-        <v>111</v>
+      <c r="E19" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F19" s="8" t="s">
+        <v>121</v>
+      </c>
+      <c r="G19" s="9" t="s">
+        <v>122</v>
+      </c>
+      <c r="H19" s="8" t="s">
+        <v>123</v>
+      </c>
+      <c r="I19" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="J19" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="K19" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="20" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B20" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D20" s="8" t="s">
+        <v>125</v>
+      </c>
+      <c r="E20" s="7" t="s">
+        <v>112</v>
+      </c>
+      <c r="F20" s="8" t="s">
+        <v>113</v>
+      </c>
+      <c r="G20" s="9" t="s">
+        <v>126</v>
+      </c>
+      <c r="H20" s="8" t="s">
+        <v>127</v>
+      </c>
+      <c r="I20" s="9" t="s">
+        <v>116</v>
+      </c>
+      <c r="J20" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="K20" s="8" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="21" spans="2:11" x14ac:dyDescent="0.3">
+      <c r="B21" s="7" t="s">
+        <v>109</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D21" s="8" t="s">
+        <v>130</v>
+      </c>
+      <c r="E21" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="F21" s="8" t="s">
+        <v>132</v>
+      </c>
+      <c r="G21" s="9" t="s">
+        <v>133</v>
+      </c>
+      <c r="H21" s="8" t="s">
+        <v>134</v>
+      </c>
+      <c r="I21" s="9" t="s">
+        <v>135</v>
+      </c>
+      <c r="J21" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="K21" s="8" t="s">
+        <v>118</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="1">
     <mergeCell ref="B1:K1"/>
   </mergeCells>
+  <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
+  <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" r:id="rId1"/>
 </worksheet>
 </file>
--- a/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_요구사항정의서.xlsx
+++ b/tmp/프로젝트 제출양식/2. 프로젝트 결과 보고서/20260428_요구사항정의서.xlsx
@@ -546,9 +546,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -557,6 +554,9 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -849,24 +849,24 @@
     <col min="6" max="6" width="15" style="5" customWidth="1"/>
     <col min="7" max="7" width="46.75" customWidth="1"/>
     <col min="8" max="8" width="20.25" style="5" customWidth="1"/>
-    <col min="9" max="9" width="18.375" customWidth="1"/>
+    <col min="9" max="9" width="20.375" customWidth="1"/>
     <col min="10" max="10" width="8" customWidth="1"/>
     <col min="11" max="11" width="10" style="5" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="2:11" ht="20.25" x14ac:dyDescent="0.3">
-      <c r="B1" s="6" t="s">
+      <c r="B1" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C1" s="6"/>
-      <c r="D1" s="6"/>
-      <c r="E1" s="6"/>
-      <c r="F1" s="6"/>
-      <c r="G1" s="6"/>
-      <c r="H1" s="6"/>
-      <c r="I1" s="6"/>
-      <c r="J1" s="6"/>
-      <c r="K1" s="6"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
+      <c r="K1" s="9"/>
     </row>
     <row r="3" spans="2:11" x14ac:dyDescent="0.3">
       <c r="B3" s="1" t="s">
@@ -1349,130 +1349,130 @@
       </c>
     </row>
     <row r="18" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B18" s="7" t="s">
+      <c r="B18" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C18" s="7" t="s">
+      <c r="C18" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="D18" s="8" t="s">
+      <c r="D18" s="7" t="s">
         <v>111</v>
       </c>
-      <c r="E18" s="7" t="s">
+      <c r="E18" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="F18" s="8" t="s">
+      <c r="F18" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="G18" s="9" t="s">
+      <c r="G18" s="8" t="s">
         <v>114</v>
       </c>
-      <c r="H18" s="8" t="s">
+      <c r="H18" s="7" t="s">
         <v>115</v>
       </c>
-      <c r="I18" s="9" t="s">
+      <c r="I18" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="J18" s="7" t="s">
+      <c r="J18" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="K18" s="8" t="s">
+      <c r="K18" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="19" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B19" s="7" t="s">
+      <c r="B19" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C19" s="7" t="s">
+      <c r="C19" s="6" t="s">
         <v>119</v>
       </c>
-      <c r="D19" s="8" t="s">
+      <c r="D19" s="7" t="s">
         <v>120</v>
       </c>
-      <c r="E19" s="7" t="s">
+      <c r="E19" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="F19" s="8" t="s">
+      <c r="F19" s="7" t="s">
         <v>121</v>
       </c>
-      <c r="G19" s="9" t="s">
+      <c r="G19" s="8" t="s">
         <v>122</v>
       </c>
-      <c r="H19" s="8" t="s">
+      <c r="H19" s="7" t="s">
         <v>123</v>
       </c>
-      <c r="I19" s="9" t="s">
+      <c r="I19" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="J19" s="7" t="s">
+      <c r="J19" s="6" t="s">
         <v>117</v>
       </c>
-      <c r="K19" s="8" t="s">
+      <c r="K19" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="20" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B20" s="7" t="s">
+      <c r="B20" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C20" s="7" t="s">
+      <c r="C20" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="D20" s="8" t="s">
+      <c r="D20" s="7" t="s">
         <v>125</v>
       </c>
-      <c r="E20" s="7" t="s">
+      <c r="E20" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="F20" s="8" t="s">
+      <c r="F20" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="G20" s="9" t="s">
+      <c r="G20" s="8" t="s">
         <v>126</v>
       </c>
-      <c r="H20" s="8" t="s">
+      <c r="H20" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="I20" s="9" t="s">
+      <c r="I20" s="8" t="s">
         <v>116</v>
       </c>
-      <c r="J20" s="7" t="s">
+      <c r="J20" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="K20" s="8" t="s">
+      <c r="K20" s="7" t="s">
         <v>118</v>
       </c>
     </row>
     <row r="21" spans="2:11" x14ac:dyDescent="0.3">
-      <c r="B21" s="7" t="s">
+      <c r="B21" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="C21" s="7" t="s">
+      <c r="C21" s="6" t="s">
         <v>129</v>
       </c>
-      <c r="D21" s="8" t="s">
+      <c r="D21" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="E21" s="7" t="s">
+      <c r="E21" s="6" t="s">
         <v>131</v>
       </c>
-      <c r="F21" s="8" t="s">
+      <c r="F21" s="7" t="s">
         <v>132</v>
       </c>
-      <c r="G21" s="9" t="s">
+      <c r="G21" s="8" t="s">
         <v>133</v>
       </c>
-      <c r="H21" s="8" t="s">
+      <c r="H21" s="7" t="s">
         <v>134</v>
       </c>
-      <c r="I21" s="9" t="s">
+      <c r="I21" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="J21" s="7" t="s">
+      <c r="J21" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="K21" s="8" t="s">
+      <c r="K21" s="7" t="s">
         <v>118</v>
       </c>
     </row>
